--- a/SAM_Opportunities_Report_20260617_PM.xlsx
+++ b/SAM_Opportunities_Report_20260617_PM.xlsx
@@ -14,10 +14,10 @@
     <sheet name="🔧 Specialty Pipeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$95</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -855,7 +855,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F26" s="26" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="F28" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F36" s="26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F38" s="26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>→  58 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
+          <t>→  57 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N95"/>
+  <dimension ref="B2:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1336,7 +1336,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>All open Solicitations sorted by urgency  ·  90 records  ·  As of June 17, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
+          <t>All open Solicitations sorted by urgency  ·  92 records  ·  As of June 17, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
         </is>
       </c>
     </row>
@@ -4357,49 +4357,49 @@
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>W9123826RA016</t>
-        </is>
-      </c>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
-        <is>
-          <t>$23.0M</t>
-        </is>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="J50" s="17" t="inlineStr">
-        <is>
-          <t>11d</t>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>36C10F26B0001</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="inlineStr">
+        <is>
+          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>San Antonio, Texas</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="G50" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>$1.5M</t>
+        </is>
+      </c>
+      <c r="I50" s="23" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>12d</t>
         </is>
       </c>
       <c r="K50" s="18" t="inlineStr">
@@ -4407,64 +4407,64 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L50" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M50" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N50" s="42" t="inlineStr">
+      <c r="L50" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
-      <c r="B51" s="33" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>36C10F26B0001</t>
-        </is>
-      </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>San Antonio, Texas</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G51" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H51" s="23" t="inlineStr">
-        <is>
-          <t>$1.5M</t>
-        </is>
-      </c>
-      <c r="I51" s="23" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>W911WN26BA014</t>
+        </is>
+      </c>
+      <c r="D51" s="37" t="inlineStr">
+        <is>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="J51" s="23" t="inlineStr">
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
@@ -4474,17 +4474,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L51" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M51" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="36" t="inlineStr">
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -4498,22 +4498,22 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="D52" s="40" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
@@ -4565,22 +4565,22 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="D53" s="37" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W912ES26QA067</t>
         </is>
       </c>
       <c r="D54" s="40" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
@@ -4692,47 +4692,47 @@
       </c>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B55" s="33" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26QA067</t>
-        </is>
-      </c>
-      <c r="D55" s="37" t="inlineStr">
-        <is>
-          <t>Fiber Optic Cable Replacement</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>36C25226Q0526</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="inlineStr">
+        <is>
+          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="23" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="J55" s="20" t="inlineStr">
+      <c r="J55" s="23" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
@@ -4742,17 +4742,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M55" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N55" s="39" t="inlineStr">
+      <c r="L55" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -4766,22 +4766,22 @@
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>36C25226Q0526</t>
+          <t>36C78626B0007</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>Madison, Wisconsin</t>
+          <t>Dayton, Ohio</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G56" s="34" t="inlineStr">
@@ -4826,49 +4826,49 @@
       </c>
     </row>
     <row r="57" ht="32" customHeight="1">
-      <c r="B57" s="33" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C57" s="23" t="inlineStr">
-        <is>
-          <t>36C78626B0007</t>
-        </is>
-      </c>
-      <c r="D57" s="28" t="inlineStr">
-        <is>
-          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="G57" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H57" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="23" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="J57" s="23" t="inlineStr">
-        <is>
-          <t>12d</t>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>140P9726R0002</t>
+        </is>
+      </c>
+      <c r="D57" s="37" t="inlineStr">
+        <is>
+          <t>Y--GLBA REHAB WATERLINE</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="20" t="inlineStr">
+        <is>
+          <t>Jul 01, 2026</t>
+        </is>
+      </c>
+      <c r="J57" s="20" t="inlineStr">
+        <is>
+          <t>13d</t>
         </is>
       </c>
       <c r="K57" s="18" t="inlineStr">
@@ -4876,17 +4876,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L57" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M57" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N57" s="36" t="inlineStr">
+      <c r="L57" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N57" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -4900,22 +4900,22 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>140P9726R0002</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="D58" s="40" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>Jul 01, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="K58" s="18" t="inlineStr">
@@ -4967,22 +4967,22 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="D59" s="37" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G59" s="20" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="I59" s="20" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>140FC226Q0036</t>
         </is>
       </c>
       <c r="D60" s="40" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -5059,22 +5059,22 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jul 03, 2026</t>
         </is>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
-        </is>
-      </c>
-      <c r="K60" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>15d</t>
+        </is>
+      </c>
+      <c r="K60" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L60" s="17" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>140FC226Q0036</t>
+          <t>89503326BWA000019</t>
         </is>
       </c>
       <c r="D61" s="37" t="inlineStr">
         <is>
-          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G61" s="20" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>Jul 03, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="J61" s="20" t="inlineStr">
         <is>
-          <t>15d</t>
+          <t>18d</t>
         </is>
       </c>
       <c r="K61" s="43" t="inlineStr">
@@ -5168,22 +5168,22 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>89503326BWA000019</t>
+          <t>191BWC26B0001</t>
         </is>
       </c>
       <c r="D62" s="40" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Tainter Gates Sandblasting</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Del Rio, Texas</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>191BWC26B0001</t>
+          <t>140FGA26R0021</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
         <is>
-          <t>Tainter Gates Sandblasting</t>
+          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>Del Rio, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I63" s="20" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0021</t>
+          <t>W9127N26BA015</t>
         </is>
       </c>
       <c r="D64" s="40" t="inlineStr">
         <is>
-          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
+          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>W9127N26BA015</t>
+          <t>140P8326Q0041</t>
         </is>
       </c>
       <c r="D65" s="37" t="inlineStr">
         <is>
-          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0041</t>
+          <t>140L3626Q0034</t>
         </is>
       </c>
       <c r="D66" s="40" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>MELSTONE DAM LIVESTOCK WATER SUPPLY</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0034</t>
+          <t>W56ZTN26BA003</t>
         </is>
       </c>
       <c r="D67" s="37" t="inlineStr">
         <is>
-          <t>MELSTONE DAM LIVESTOCK WATER SUPPLY</t>
+          <t>Unidirectional Hydrant Flushing and Repair Program</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
@@ -5570,22 +5570,22 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>W56ZTN26BA003</t>
+          <t>W9127826RA046</t>
         </is>
       </c>
       <c r="D68" s="40" t="inlineStr">
         <is>
-          <t>Unidirectional Hydrant Flushing and Repair Program</t>
+          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Biloxi, Mississippi</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t>18d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="K68" s="43" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA046</t>
+          <t>W912P926BA007</t>
         </is>
       </c>
       <c r="D69" s="37" t="inlineStr">
         <is>
-          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
+          <t>Crains Island Stage 3</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Biloxi, Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -5704,22 +5704,22 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>W912P926BA007</t>
+          <t>W9128F26BA019</t>
         </is>
       </c>
       <c r="D70" s="40" t="inlineStr">
         <is>
-          <t>Crains Island Stage 3</t>
+          <t>Oahe IDCC Road Maintenance 2026</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Pierre, South Dakota</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>W9128F26BA019</t>
+          <t>FA282326R0014</t>
         </is>
       </c>
       <c r="D71" s="37" t="inlineStr">
         <is>
-          <t>Oahe IDCC Road Maintenance 2026</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>Fort Pierre, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>FA282326R0014</t>
+          <t>140P5326R0006</t>
         </is>
       </c>
       <c r="D72" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
+          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="K72" s="43" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>140P5326R0006</t>
+          <t>140P6426B0008</t>
         </is>
       </c>
       <c r="D73" s="37" t="inlineStr">
         <is>
-          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
+          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G73" s="20" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0008</t>
+          <t>140FC226Q0038</t>
         </is>
       </c>
       <c r="D74" s="40" t="inlineStr">
         <is>
-          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
+          <t>MN-UPR MS RIV NATL WILDL-WELL REPAIRS</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
@@ -6508,22 +6508,22 @@
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>W9124D26QA266</t>
+          <t>W9123826RA016</t>
         </is>
       </c>
       <c r="D82" s="40" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="I82" s="17" t="inlineStr">
@@ -6575,17 +6575,17 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0037</t>
+          <t>W9124D26QA266</t>
         </is>
       </c>
       <c r="D83" s="37" t="inlineStr">
         <is>
-          <t>Pompeys Pillar Security System Upgrade</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>140L3626Q0037</t>
         </is>
       </c>
       <c r="D84" s="40" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Pompeys Pillar Security System Upgrade</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="K84" s="43" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="D85" s="37" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G85" s="20" t="inlineStr">
@@ -6776,22 +6776,22 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>75F40126R00051</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="D86" s="40" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
@@ -6843,22 +6843,22 @@
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>140P2026R0011</t>
+          <t>75F40126R00051</t>
         </is>
       </c>
       <c r="D87" s="37" t="inlineStr">
         <is>
-          <t>GLCA Hite</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G87" s="20" t="inlineStr">
@@ -6910,127 +6910,127 @@
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
+          <t>140P2026R0011</t>
+        </is>
+      </c>
+      <c r="D88" s="40" t="inlineStr">
+        <is>
+          <t>GLCA Hite</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>27d</t>
+        </is>
+      </c>
+      <c r="K88" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
           <t>W9127826RA059</t>
         </is>
       </c>
-      <c r="D88" s="40" t="inlineStr">
+      <c r="D89" s="37" t="inlineStr">
         <is>
           <t>Water Tank Storage</t>
         </is>
       </c>
-      <c r="E88" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F88" s="17" t="inlineStr">
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="G88" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H88" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="20" t="inlineStr">
         <is>
           <t>Jul 16, 2026</t>
         </is>
       </c>
-      <c r="J88" s="17" t="inlineStr">
+      <c r="J89" s="20" t="inlineStr">
         <is>
           <t>28d</t>
         </is>
       </c>
-      <c r="K88" s="43" t="inlineStr">
+      <c r="K89" s="43" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L88" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="32" customHeight="1">
-      <c r="B89" s="33" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="inlineStr">
-        <is>
-          <t>W50S6T26QA026</t>
-        </is>
-      </c>
-      <c r="D89" s="28" t="inlineStr">
-        <is>
-          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G89" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t>$25K</t>
-        </is>
-      </c>
-      <c r="I89" s="23" t="inlineStr">
-        <is>
-          <t>Jul 17, 2026</t>
-        </is>
-      </c>
-      <c r="J89" s="23" t="inlineStr">
-        <is>
-          <t>29d</t>
-        </is>
-      </c>
-      <c r="K89" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L89" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M89" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N89" s="36" t="inlineStr">
+      <c r="L89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M89" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -7044,22 +7044,22 @@
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>W912HN26BA008</t>
         </is>
       </c>
       <c r="D90" s="40" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -7069,22 +7069,22 @@
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>Jul 20, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
         <is>
-          <t>32d</t>
-        </is>
-      </c>
-      <c r="K90" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K90" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L90" s="17" t="inlineStr">
@@ -7111,22 +7111,22 @@
       </c>
       <c r="C91" s="23" t="inlineStr">
         <is>
-          <t>36C25626R0015</t>
+          <t>W50S6T26QA026</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
         <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Fayetteville, Arkansas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G91" s="34" t="inlineStr">
@@ -7136,22 +7136,22 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t>$15.0M</t>
+          <t>$25K</t>
         </is>
       </c>
       <c r="I91" s="23" t="inlineStr">
         <is>
-          <t>Jul 23, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="J91" s="23" t="inlineStr">
         <is>
-          <t>35d</t>
-        </is>
-      </c>
-      <c r="K91" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K91" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L91" s="23" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>127EAX26R0006</t>
+          <t>75H70126R00030</t>
         </is>
       </c>
       <c r="D92" s="40" t="inlineStr">
         <is>
-          <t>R3 National Forest’s Roads IDIQ</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G92" s="17" t="inlineStr">
@@ -7203,17 +7203,17 @@
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>$72.5M</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 20, 2026</t>
         </is>
       </c>
       <c r="J92" s="17" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="K92" s="44" t="inlineStr">
@@ -7238,67 +7238,67 @@
       </c>
     </row>
     <row r="93" ht="32" customHeight="1">
-      <c r="B93" s="20" t="inlineStr">
+      <c r="B93" s="33" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="C93" s="20" t="inlineStr">
-        <is>
-          <t>FA850126R0004</t>
-        </is>
-      </c>
-      <c r="D93" s="37" t="inlineStr">
-        <is>
-          <t>Robins AFB Paving Multi-Award IDIQ</t>
-        </is>
-      </c>
-      <c r="E93" s="20" t="inlineStr">
-        <is>
-          <t>Warner Robins, Georgia</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G93" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="inlineStr">
-        <is>
-          <t>$45.0M</t>
-        </is>
-      </c>
-      <c r="I93" s="20" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="J93" s="20" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K93" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
-        </is>
-      </c>
-      <c r="L93" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M93" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N93" s="39" t="inlineStr">
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="D93" s="28" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="E93" s="23" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G93" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="I93" s="23" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="J93" s="23" t="inlineStr">
+        <is>
+          <t>35d</t>
+        </is>
+      </c>
+      <c r="K93" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
+        </is>
+      </c>
+      <c r="L93" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>140FGA26Q0029</t>
+          <t>127EAX26R0006</t>
         </is>
       </c>
       <c r="D94" s="40" t="inlineStr">
         <is>
-          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
+          <t>R3 National Forest’s Roads IDIQ</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G94" s="17" t="inlineStr">
@@ -7337,22 +7337,22 @@
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$72.5M</t>
         </is>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K94" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>36d</t>
+        </is>
+      </c>
+      <c r="K94" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="L94" s="17" t="inlineStr">
@@ -7379,67 +7379,201 @@
       </c>
       <c r="C95" s="20" t="inlineStr">
         <is>
+          <t>FA850126R0004</t>
+        </is>
+      </c>
+      <c r="D95" s="37" t="inlineStr">
+        <is>
+          <t>Robins AFB Paving Multi-Award IDIQ</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>Warner Robins, Georgia</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="I95" s="20" t="inlineStr">
+        <is>
+          <t>Jun 18, 2026</t>
+        </is>
+      </c>
+      <c r="J95" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K95" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L95" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M95" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>140FGA26Q0029</t>
+        </is>
+      </c>
+      <c r="D96" s="40" t="inlineStr">
+        <is>
+          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>Jun 18, 2026</t>
+        </is>
+      </c>
+      <c r="J96" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K96" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L96" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N96" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C97" s="20" t="inlineStr">
+        <is>
           <t>W912WJ26QA113</t>
         </is>
       </c>
-      <c r="D95" s="37" t="inlineStr">
+      <c r="D97" s="37" t="inlineStr">
         <is>
           <t>Drainage Basin Installation, Mansfield Hollow Dam, Mansfield, CT</t>
         </is>
       </c>
-      <c r="E95" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F95" s="20" t="inlineStr">
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="G95" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H95" s="20" t="inlineStr">
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H97" s="20" t="inlineStr">
         <is>
           <t>$62K</t>
         </is>
       </c>
-      <c r="I95" s="20" t="inlineStr">
+      <c r="I97" s="20" t="inlineStr">
         <is>
           <t>Jun 18, 2026</t>
         </is>
       </c>
-      <c r="J95" s="20" t="inlineStr">
+      <c r="J97" s="20" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K95" s="18" t="inlineStr">
+      <c r="K97" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L95" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M95" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N95" s="39" t="inlineStr">
+      <c r="L97" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M97" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N97" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:N95"/>
+  <autoFilter ref="B5:N97"/>
   <mergeCells count="2">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -7535,6 +7669,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N93" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N97" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7547,7 +7683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K52"/>
+  <dimension ref="B2:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7575,7 +7711,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Early-stage opportunities to monitor  ·  47 records  (6 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
+          <t>Early-stage opportunities to monitor  ·  48 records  (6 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
         </is>
       </c>
     </row>
@@ -8415,22 +8551,22 @@
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>W50S7X-26-B-A003</t>
+          <t>140R6026R0016</t>
         </is>
       </c>
       <c r="C21" s="37" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -8440,22 +8576,22 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>$7.5M</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>53d</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -8467,12 +8603,12 @@
     <row r="22" ht="32" customHeight="1">
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>W9133L26BA010</t>
+          <t>W50S7X-26-B-A003</t>
         </is>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
-          <t>Air National Guard (ANG) Smart Meters</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
@@ -8492,17 +8628,17 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>$4.2M</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
@@ -8519,12 +8655,12 @@
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W9133L26BA010</t>
         </is>
       </c>
       <c r="C23" s="37" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>Air National Guard (ANG) Smart Meters</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -8534,7 +8670,7 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -8544,17 +8680,17 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$4.2M</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -8571,12 +8707,12 @@
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>W912DR26BA007</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -8601,12 +8737,12 @@
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J24" s="17" t="inlineStr">
@@ -8623,22 +8759,22 @@
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00029</t>
+          <t>W912DR26BA007</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -8653,12 +8789,12 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -8675,22 +8811,22 @@
     <row r="26" ht="32" customHeight="1">
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>W912WJ26QA124</t>
+          <t>75H70126R00029</t>
         </is>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -8700,17 +8836,17 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="J26" s="17" t="inlineStr">
@@ -8727,22 +8863,22 @@
     <row r="27" ht="32" customHeight="1">
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>140P6026Q0052</t>
+          <t>W912WJ26QA124</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -8752,17 +8888,17 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -8779,22 +8915,22 @@
     <row r="28" ht="32" customHeight="1">
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>12445526Q0069</t>
+          <t>140P6026Q0052</t>
         </is>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -8804,22 +8940,22 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>$25K</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
@@ -8831,17 +8967,17 @@
     <row r="29" ht="32" customHeight="1">
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA025</t>
+          <t>12445526Q0069</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>Phillips Parkway Haul Route</t>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>Cape Canaveral, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -8856,17 +8992,17 @@
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$25K</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -8883,22 +9019,22 @@
     <row r="30" ht="32" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>W9127826RA025</t>
         </is>
       </c>
       <c r="C30" s="40" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Cape Canaveral, Florida</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -8923,7 +9059,7 @@
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
@@ -8935,12 +9071,12 @@
     <row r="31" ht="32" customHeight="1">
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -8950,7 +9086,7 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -8965,17 +9101,17 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -8987,12 +9123,12 @@
     <row r="32" ht="32" customHeight="1">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>SP470525R002026</t>
         </is>
       </c>
       <c r="C32" s="40" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -9002,7 +9138,7 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
@@ -9017,17 +9153,17 @@
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
@@ -9039,12 +9175,12 @@
     <row r="33" ht="32" customHeight="1">
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -9091,12 +9227,12 @@
     <row r="34" ht="32" customHeight="1">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>36C25226Q0426</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C34" s="40" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -9106,7 +9242,7 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -9121,12 +9257,12 @@
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
@@ -9143,12 +9279,12 @@
     <row r="35" ht="32" customHeight="1">
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>W911WN26RA011</t>
+          <t>36C25226Q0426</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
         <is>
-          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -9158,7 +9294,7 @@
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -9173,12 +9309,12 @@
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -9195,12 +9331,12 @@
     <row r="36" ht="32" customHeight="1">
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>140L2626R0004</t>
+          <t>W911WN26RA011</t>
         </is>
       </c>
       <c r="C36" s="40" t="inlineStr">
         <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
+          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
@@ -9225,12 +9361,12 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J36" s="17" t="inlineStr">
@@ -9247,12 +9383,12 @@
     <row r="37" ht="32" customHeight="1">
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>140L2626Q0032</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C37" s="37" t="inlineStr">
         <is>
-          <t>Y--Indian Springs Vault Toilet</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -9299,12 +9435,12 @@
     <row r="38" ht="32" customHeight="1">
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C38" s="40" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>Y--Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
@@ -9314,7 +9450,7 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
@@ -9329,12 +9465,12 @@
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
@@ -9351,12 +9487,12 @@
     <row r="39" ht="32" customHeight="1">
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C39" s="37" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -9366,7 +9502,7 @@
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -9403,12 +9539,12 @@
     <row r="40" ht="32" customHeight="1">
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C40" s="40" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
@@ -9433,12 +9569,12 @@
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="J40" s="17" t="inlineStr">
@@ -9455,22 +9591,22 @@
     <row r="41" ht="32" customHeight="1">
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>W912EE26RA015</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C41" s="37" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -9485,12 +9621,12 @@
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J41" s="20" t="inlineStr">
@@ -9507,17 +9643,17 @@
     <row r="42" ht="32" customHeight="1">
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>36C24526Q0576</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C42" s="40" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
@@ -9537,12 +9673,12 @@
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J42" s="17" t="inlineStr">
@@ -9559,22 +9695,22 @@
     <row r="43" ht="32" customHeight="1">
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>36C24526Q0576</t>
         </is>
       </c>
       <c r="C43" s="37" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -9589,12 +9725,12 @@
       </c>
       <c r="H43" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr">
@@ -9611,12 +9747,12 @@
     <row r="44" ht="32" customHeight="1">
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C44" s="40" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
@@ -9626,7 +9762,7 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -9663,12 +9799,12 @@
     <row r="45" ht="32" customHeight="1">
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C45" s="37" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -9678,7 +9814,7 @@
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -9715,22 +9851,22 @@
     <row r="46" ht="32" customHeight="1">
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>140P6326B0008</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C46" s="40" t="inlineStr">
         <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>Medora, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
@@ -9745,12 +9881,12 @@
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J46" s="17" t="inlineStr">
@@ -9767,17 +9903,17 @@
     <row r="47" ht="32" customHeight="1">
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>140P8526Q0083</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C47" s="37" t="inlineStr">
         <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E47" s="20" t="inlineStr">
@@ -9797,12 +9933,12 @@
       </c>
       <c r="H47" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J47" s="20" t="inlineStr">
@@ -9819,12 +9955,12 @@
     <row r="48" ht="32" customHeight="1">
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>140P9726Q0046</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C48" s="40" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -9834,7 +9970,7 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
@@ -9871,22 +10007,22 @@
     <row r="49" ht="32" customHeight="1">
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>W50S85-26-B-A007</t>
+          <t>140P9726Q0046</t>
         </is>
       </c>
       <c r="C49" s="37" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
@@ -9901,12 +10037,12 @@
       </c>
       <c r="H49" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J49" s="20" t="inlineStr">
@@ -9923,22 +10059,22 @@
     <row r="50" ht="32" customHeight="1">
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>W912DQ26QA063</t>
+          <t>W50S85-26-B-A007</t>
         </is>
       </c>
       <c r="C50" s="40" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -9953,12 +10089,12 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J50" s="17" t="inlineStr">
@@ -9975,17 +10111,17 @@
     <row r="51" ht="32" customHeight="1">
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>140R4025R0017</t>
+          <t>W912DQ26QA063</t>
         </is>
       </c>
       <c r="C51" s="37" t="inlineStr">
         <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stockton, Missouri</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
@@ -10005,12 +10141,12 @@
       </c>
       <c r="H51" s="20" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I51" s="20" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J51" s="20" t="inlineStr">
@@ -10027,57 +10163,109 @@
     <row r="52" ht="32" customHeight="1">
       <c r="B52" s="17" t="inlineStr">
         <is>
+          <t>140R4025R0017</t>
+        </is>
+      </c>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>28d</t>
+        </is>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="B53" s="20" t="inlineStr">
+        <is>
           <t>W15QKN26RA070</t>
         </is>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>W15QKN-26-R-A070 - Sources Sought for Building 602 Motor Pool Full Depth Reclamation and Paving at Fort Devens, MA</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="17" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
         <is>
           <t>Jun 24, 2026</t>
         </is>
       </c>
-      <c r="I52" s="17" t="inlineStr">
+      <c r="I53" s="20" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="J52" s="17" t="inlineStr">
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K52" s="17" t="inlineStr">
+      <c r="K53" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K52"/>
+  <autoFilter ref="B5:K53"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -10093,7 +10281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K142"/>
+  <dimension ref="B2:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10121,7 +10309,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Complete data  ·  137 records  ·  June 17, 2026</t>
+          <t>Complete data  ·  140 records  ·  June 17, 2026</t>
         </is>
       </c>
     </row>
@@ -12467,104 +12655,104 @@
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>W9123826RA016</t>
-        </is>
-      </c>
-      <c r="C50" s="40" t="inlineStr">
-        <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>$23.0M</t>
-        </is>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
-        <is>
-          <t>Jun 29, 2026</t>
-        </is>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>11d</t>
-        </is>
-      </c>
-      <c r="J50" s="17" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>36C10F26B0001</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
+        <is>
+          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>San Antonio, Texas</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>$1.5M</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I50" s="23" t="inlineStr">
+        <is>
+          <t>12d</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K50" s="42" t="inlineStr">
+      <c r="K50" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="B51" s="23" t="inlineStr">
-        <is>
-          <t>36C10F26B0001</t>
-        </is>
-      </c>
-      <c r="C51" s="28" t="inlineStr">
-        <is>
-          <t>Fort Sam Houston National Cemetery, Phase 3 Expansion - Additional Road Repairs</t>
-        </is>
-      </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>San Antonio, Texas</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t>$1.5M</t>
-        </is>
-      </c>
-      <c r="H51" s="23" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>W911WN26BA014</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="inlineStr">
+        <is>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I51" s="23" t="inlineStr">
+      <c r="I51" s="20" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
       </c>
-      <c r="J51" s="23" t="inlineStr">
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K51" s="36" t="inlineStr">
+      <c r="K51" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12573,22 +12761,22 @@
     <row r="52" ht="28" customHeight="1">
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="C52" s="40" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
@@ -12598,7 +12786,7 @@
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
@@ -12625,22 +12813,22 @@
     <row r="53" ht="28" customHeight="1">
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="C53" s="37" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
@@ -12677,17 +12865,17 @@
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W912ES26QA067</t>
         </is>
       </c>
       <c r="C54" s="40" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
@@ -12727,52 +12915,52 @@
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26QA067</t>
-        </is>
-      </c>
-      <c r="C55" s="37" t="inlineStr">
-        <is>
-          <t>Fiber Optic Cable Replacement</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>36C25226Q0526</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="I55" s="23" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
       </c>
-      <c r="J55" s="20" t="inlineStr">
+      <c r="J55" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K55" s="39" t="inlineStr">
+      <c r="K55" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12781,22 +12969,22 @@
     <row r="56" ht="28" customHeight="1">
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>36C25226Q0526</t>
+          <t>36C78626B0007</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>Madison, Wisconsin</t>
+          <t>Dayton, Ohio</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
@@ -12831,52 +13019,52 @@
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="B57" s="23" t="inlineStr">
-        <is>
-          <t>36C78626B0007</t>
-        </is>
-      </c>
-      <c r="C57" s="28" t="inlineStr">
-        <is>
-          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
-        </is>
-      </c>
-      <c r="D57" s="23" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="23" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I57" s="23" t="inlineStr">
-        <is>
-          <t>12d</t>
-        </is>
-      </c>
-      <c r="J57" s="23" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>140P9726R0002</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="inlineStr">
+        <is>
+          <t>Y--GLBA REHAB WATERLINE</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>Jul 01, 2026</t>
+        </is>
+      </c>
+      <c r="I57" s="20" t="inlineStr">
+        <is>
+          <t>13d</t>
+        </is>
+      </c>
+      <c r="J57" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K57" s="36" t="inlineStr">
+      <c r="K57" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -12885,22 +13073,22 @@
     <row r="58" ht="28" customHeight="1">
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>140P9726R0002</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
@@ -12915,12 +13103,12 @@
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>Jul 01, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J58" s="17" t="inlineStr">
@@ -12937,22 +13125,22 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="C59" s="37" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
@@ -12962,7 +13150,7 @@
       </c>
       <c r="G59" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="H59" s="20" t="inlineStr">
@@ -12989,12 +13177,12 @@
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>140FC226Q0036</t>
         </is>
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -13004,7 +13192,7 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -13014,17 +13202,17 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jul 03, 2026</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>15d</t>
         </is>
       </c>
       <c r="J60" s="17" t="inlineStr">
@@ -13041,12 +13229,12 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>140FC226Q0036</t>
+          <t>89503326BWA000019</t>
         </is>
       </c>
       <c r="C61" s="37" t="inlineStr">
         <is>
-          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -13056,7 +13244,7 @@
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
@@ -13071,12 +13259,12 @@
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>Jul 03, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>15d</t>
+          <t>18d</t>
         </is>
       </c>
       <c r="J61" s="20" t="inlineStr">
@@ -13093,22 +13281,22 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>89503326BWA000019</t>
+          <t>191BWC26B0001</t>
         </is>
       </c>
       <c r="C62" s="40" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Tainter Gates Sandblasting</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Del Rio, Texas</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
@@ -13118,7 +13306,7 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
@@ -13145,17 +13333,17 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>191BWC26B0001</t>
+          <t>140FGA26R0021</t>
         </is>
       </c>
       <c r="C63" s="37" t="inlineStr">
         <is>
-          <t>Tainter Gates Sandblasting</t>
+          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>Del Rio, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
@@ -13170,7 +13358,7 @@
       </c>
       <c r="G63" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H63" s="20" t="inlineStr">
@@ -13197,12 +13385,12 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0021</t>
+          <t>W9127N26BA015</t>
         </is>
       </c>
       <c r="C64" s="40" t="inlineStr">
         <is>
-          <t>Y--MI-SENEY NWR-DC DAM DECOMMISIONING</t>
+          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -13249,12 +13437,12 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>W9127N26BA015</t>
+          <t>140P8326Q0041</t>
         </is>
       </c>
       <c r="C65" s="37" t="inlineStr">
         <is>
-          <t>Oregon/Washington Clamshell Maintenance Dredging 2026</t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -13264,7 +13452,7 @@
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
@@ -13301,12 +13489,12 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0041</t>
+          <t>140L3626Q0034</t>
         </is>
       </c>
       <c r="C66" s="40" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>MELSTONE DAM LIVESTOCK WATER SUPPLY</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -13316,7 +13504,7 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
@@ -13353,12 +13541,12 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0034</t>
+          <t>W56ZTN26BA003</t>
         </is>
       </c>
       <c r="C67" s="37" t="inlineStr">
         <is>
-          <t>MELSTONE DAM LIVESTOCK WATER SUPPLY</t>
+          <t>Unidirectional Hydrant Flushing and Repair Program</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -13378,7 +13566,7 @@
       </c>
       <c r="G67" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H67" s="20" t="inlineStr">
@@ -13405,22 +13593,22 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>W56ZTN26BA003</t>
+          <t>W9127826RA046</t>
         </is>
       </c>
       <c r="C68" s="40" t="inlineStr">
         <is>
-          <t>Unidirectional Hydrant Flushing and Repair Program</t>
+          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Biloxi, Mississippi</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
@@ -13430,17 +13618,17 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>18d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="J68" s="17" t="inlineStr">
@@ -13457,17 +13645,17 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA046</t>
+          <t>W912P926BA007</t>
         </is>
       </c>
       <c r="C69" s="37" t="inlineStr">
         <is>
-          <t>Deer Island Ecosystem Restoration, Phase 1 Deer Island, MS (Harrison County)</t>
+          <t>Crains Island Stage 3</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>Biloxi, Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
@@ -13509,22 +13697,22 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>W912P926BA007</t>
+          <t>W9128F26BA019</t>
         </is>
       </c>
       <c r="C70" s="40" t="inlineStr">
         <is>
-          <t>Crains Island Stage 3</t>
+          <t>Oahe IDCC Road Maintenance 2026</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Pierre, South Dakota</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
@@ -13561,22 +13749,22 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>W9128F26BA019</t>
+          <t>FA282326R0014</t>
         </is>
       </c>
       <c r="C71" s="37" t="inlineStr">
         <is>
-          <t>Oahe IDCC Road Maintenance 2026</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>Fort Pierre, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
@@ -13613,12 +13801,12 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>FA282326R0014</t>
+          <t>140P5326R0006</t>
         </is>
       </c>
       <c r="C72" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
+          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
@@ -13628,7 +13816,7 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
@@ -13643,12 +13831,12 @@
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J72" s="17" t="inlineStr">
@@ -13665,12 +13853,12 @@
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>140P5326R0006</t>
+          <t>140P6426B0008</t>
         </is>
       </c>
       <c r="C73" s="37" t="inlineStr">
         <is>
-          <t>MACA-REHAB ENTRANCE SIGNS/PARKING AREAS</t>
+          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -13680,7 +13868,7 @@
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
@@ -13717,12 +13905,12 @@
     <row r="74" ht="28" customHeight="1">
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0008</t>
+          <t>140FC226Q0038</t>
         </is>
       </c>
       <c r="C74" s="40" t="inlineStr">
         <is>
-          <t>Z--ZION- Crawford Dam Removal and Diversion</t>
+          <t>MN-UPR MS RIV NATL WILDL-WELL REPAIRS</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
@@ -13732,7 +13920,7 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
@@ -14133,22 +14321,22 @@
     <row r="82" ht="28" customHeight="1">
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>W9124D26QA266</t>
+          <t>W9123826RA016</t>
         </is>
       </c>
       <c r="C82" s="40" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
@@ -14158,7 +14346,7 @@
       </c>
       <c r="G82" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="H82" s="17" t="inlineStr">
@@ -14185,17 +14373,17 @@
     <row r="83" ht="28" customHeight="1">
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0037</t>
+          <t>W9124D26QA266</t>
         </is>
       </c>
       <c r="C83" s="37" t="inlineStr">
         <is>
-          <t>Pompeys Pillar Security System Upgrade</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
@@ -14237,12 +14425,12 @@
     <row r="84" ht="28" customHeight="1">
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>140L3626Q0037</t>
         </is>
       </c>
       <c r="C84" s="40" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Pompeys Pillar Security System Upgrade</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
@@ -14252,7 +14440,7 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -14267,12 +14455,12 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
@@ -14289,12 +14477,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="C85" s="37" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -14304,7 +14492,7 @@
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
@@ -14341,22 +14529,22 @@
     <row r="86" ht="28" customHeight="1">
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>75F40126R00051</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="C86" s="40" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -14393,22 +14581,22 @@
     <row r="87" ht="28" customHeight="1">
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>140P2026R0011</t>
+          <t>75F40126R00051</t>
         </is>
       </c>
       <c r="C87" s="37" t="inlineStr">
         <is>
-          <t>GLCA Hite</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
@@ -14445,102 +14633,102 @@
     <row r="88" ht="28" customHeight="1">
       <c r="B88" s="17" t="inlineStr">
         <is>
+          <t>140P2026R0011</t>
+        </is>
+      </c>
+      <c r="C88" s="40" t="inlineStr">
+        <is>
+          <t>GLCA Hite</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>27d</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K88" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="B89" s="20" t="inlineStr">
+        <is>
           <t>W9127826RA059</t>
         </is>
       </c>
-      <c r="C88" s="40" t="inlineStr">
+      <c r="C89" s="37" t="inlineStr">
         <is>
           <t>Water Tank Storage</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E88" s="17" t="inlineStr">
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F88" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G88" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H88" s="17" t="inlineStr">
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
         <is>
           <t>Jul 16, 2026</t>
         </is>
       </c>
-      <c r="I88" s="17" t="inlineStr">
+      <c r="I89" s="20" t="inlineStr">
         <is>
           <t>28d</t>
         </is>
       </c>
-      <c r="J88" s="17" t="inlineStr">
+      <c r="J89" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K88" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>W50S6T26QA026</t>
-        </is>
-      </c>
-      <c r="C89" s="28" t="inlineStr">
-        <is>
-          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
-        </is>
-      </c>
-      <c r="D89" s="23" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t>$25K</t>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t>Jul 17, 2026</t>
-        </is>
-      </c>
-      <c r="I89" s="23" t="inlineStr">
-        <is>
-          <t>29d</t>
-        </is>
-      </c>
-      <c r="J89" s="23" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K89" s="36" t="inlineStr">
+      <c r="K89" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14549,22 +14737,22 @@
     <row r="90" ht="28" customHeight="1">
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>W912HN26BA008</t>
         </is>
       </c>
       <c r="C90" s="40" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -14574,17 +14762,17 @@
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>Jul 20, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
@@ -14601,22 +14789,22 @@
     <row r="91" ht="28" customHeight="1">
       <c r="B91" s="23" t="inlineStr">
         <is>
-          <t>36C25626R0015</t>
+          <t>W50S6T26QA026</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
         <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
         </is>
       </c>
       <c r="D91" s="23" t="inlineStr">
         <is>
-          <t>Fayetteville, Arkansas</t>
+          <t>California</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
@@ -14626,17 +14814,17 @@
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
-          <t>$15.0M</t>
+          <t>$25K</t>
         </is>
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t>Jul 23, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="I91" s="23" t="inlineStr">
         <is>
-          <t>35d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J91" s="23" t="inlineStr">
@@ -14653,22 +14841,22 @@
     <row r="92" ht="28" customHeight="1">
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>127EAX26R0006</t>
+          <t>75H70126R00030</t>
         </is>
       </c>
       <c r="C92" s="40" t="inlineStr">
         <is>
-          <t>R3 National Forest’s Roads IDIQ</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -14678,17 +14866,17 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>$72.5M</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 20, 2026</t>
         </is>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="J92" s="17" t="inlineStr">
@@ -14703,52 +14891,52 @@
       </c>
     </row>
     <row r="93" ht="28" customHeight="1">
-      <c r="B93" s="20" t="inlineStr">
-        <is>
-          <t>FA850126R0004</t>
-        </is>
-      </c>
-      <c r="C93" s="37" t="inlineStr">
-        <is>
-          <t>Robins AFB Paving Multi-Award IDIQ</t>
-        </is>
-      </c>
-      <c r="D93" s="20" t="inlineStr">
-        <is>
-          <t>Warner Robins, Georgia</t>
-        </is>
-      </c>
-      <c r="E93" s="20" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G93" s="20" t="inlineStr">
-        <is>
-          <t>$45.0M</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I93" s="20" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J93" s="20" t="inlineStr">
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="C93" s="28" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="D93" s="23" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="E93" s="23" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="I93" s="23" t="inlineStr">
+        <is>
+          <t>35d</t>
+        </is>
+      </c>
+      <c r="J93" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K93" s="39" t="inlineStr">
+      <c r="K93" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14757,12 +14945,12 @@
     <row r="94" ht="28" customHeight="1">
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>140FGA26Q0029</t>
+          <t>127EAX26R0006</t>
         </is>
       </c>
       <c r="C94" s="40" t="inlineStr">
         <is>
-          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
+          <t>R3 National Forest’s Roads IDIQ</t>
         </is>
       </c>
       <c r="D94" s="17" t="inlineStr">
@@ -14772,7 +14960,7 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -14782,17 +14970,17 @@
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$72.5M</t>
         </is>
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
@@ -14809,22 +14997,22 @@
     <row r="95" ht="28" customHeight="1">
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>W912WJ26QA113</t>
+          <t>FA850126R0004</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
         <is>
-          <t>Drainage Basin Installation, Mansfield Hollow Dam, Mansfield, CT</t>
+          <t>Robins AFB Paving Multi-Award IDIQ</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Warner Robins, Georgia</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
@@ -14834,7 +15022,7 @@
       </c>
       <c r="G95" s="20" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H95" s="20" t="inlineStr">
@@ -14861,12 +15049,12 @@
     <row r="96" ht="28" customHeight="1">
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>36C25226Q0426</t>
+          <t>140FGA26Q0029</t>
         </is>
       </c>
       <c r="C96" s="40" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
         </is>
       </c>
       <c r="D96" s="17" t="inlineStr">
@@ -14891,17 +15079,17 @@
       </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J96" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K96" s="42" t="inlineStr">
@@ -14913,22 +15101,22 @@
     <row r="97" ht="28" customHeight="1">
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>36C24526Q0576</t>
+          <t>W912WJ26QA113</t>
         </is>
       </c>
       <c r="C97" s="37" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Drainage Basin Installation, Mansfield Hollow Dam, Mansfield, CT</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -14938,22 +15126,22 @@
       </c>
       <c r="G97" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="H97" s="20" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K97" s="39" t="inlineStr">
@@ -14965,22 +15153,22 @@
     <row r="98" ht="28" customHeight="1">
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>FDA-PRESOL-132892</t>
+          <t>36C25226Q0426</t>
         </is>
       </c>
       <c r="C98" s="40" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
@@ -14990,7 +15178,7 @@
       </c>
       <c r="G98" s="17" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H98" s="17" t="inlineStr">
@@ -15017,22 +15205,22 @@
     <row r="99" ht="28" customHeight="1">
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>36C24526Q0576</t>
         </is>
       </c>
       <c r="C99" s="37" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -15047,12 +15235,12 @@
       </c>
       <c r="H99" s="20" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
@@ -15069,22 +15257,22 @@
     <row r="100" ht="28" customHeight="1">
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>W50S7X-26-B-A003</t>
+          <t>FDA-PRESOL-132892</t>
         </is>
       </c>
       <c r="C100" s="40" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
@@ -15094,17 +15282,17 @@
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="J100" s="17" t="inlineStr">
@@ -15121,17 +15309,17 @@
     <row r="101" ht="28" customHeight="1">
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>GROUP1-24-R-W001</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
@@ -15146,17 +15334,17 @@
       </c>
       <c r="G101" s="20" t="inlineStr">
         <is>
-          <t>$17.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H101" s="20" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
@@ -15171,52 +15359,52 @@
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
-      <c r="B102" s="23" t="inlineStr">
-        <is>
-          <t>36C26126R0050</t>
-        </is>
-      </c>
-      <c r="C102" s="28" t="inlineStr">
-        <is>
-          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
-        </is>
-      </c>
-      <c r="D102" s="23" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
-      <c r="E102" s="23" t="inlineStr">
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>W50S7X-26-B-A003</t>
+        </is>
+      </c>
+      <c r="C102" s="40" t="inlineStr">
+        <is>
+          <t>B16 PLC Replacement</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F102" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G102" s="23" t="inlineStr">
-        <is>
-          <t>$5.0M</t>
-        </is>
-      </c>
-      <c r="H102" s="23" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I102" s="23" t="inlineStr">
-        <is>
-          <t>6d</t>
-        </is>
-      </c>
-      <c r="J102" s="23" t="inlineStr">
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>$5.1M</t>
+        </is>
+      </c>
+      <c r="H102" s="17" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="J102" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K102" s="36" t="inlineStr">
+      <c r="K102" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15225,22 +15413,22 @@
     <row r="103" ht="28" customHeight="1">
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>W15QKN26RA070</t>
+          <t>GROUP1-24-R-W001</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
         <is>
-          <t>W15QKN-26-R-A070 - Sources Sought for Building 602 Motor Pool Full Depth Reclamation and Paving at Fort Devens, MA</t>
+          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15250,7 +15438,7 @@
       </c>
       <c r="G103" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$17.5M</t>
         </is>
       </c>
       <c r="H103" s="20" t="inlineStr">
@@ -15275,52 +15463,52 @@
       </c>
     </row>
     <row r="104" ht="28" customHeight="1">
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>140P8526Q0083</t>
-        </is>
-      </c>
-      <c r="C104" s="40" t="inlineStr">
-        <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
-        </is>
-      </c>
-      <c r="D104" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E104" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F104" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G104" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H104" s="17" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>7d</t>
-        </is>
-      </c>
-      <c r="J104" s="17" t="inlineStr">
+      <c r="B104" s="23" t="inlineStr">
+        <is>
+          <t>36C26126R0050</t>
+        </is>
+      </c>
+      <c r="C104" s="28" t="inlineStr">
+        <is>
+          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
+        </is>
+      </c>
+      <c r="D104" s="23" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="E104" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F104" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr">
+        <is>
+          <t>$5.0M</t>
+        </is>
+      </c>
+      <c r="H104" s="23" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I104" s="23" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="J104" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K104" s="42" t="inlineStr">
+      <c r="K104" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15329,12 +15517,12 @@
     <row r="105" ht="28" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>140P9726Q0046</t>
+          <t>W15QKN26RA070</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>W15QKN-26-R-A070 - Sources Sought for Building 602 Motor Pool Full Depth Reclamation and Paving at Fort Devens, MA</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -15344,7 +15532,7 @@
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -15359,12 +15547,12 @@
       </c>
       <c r="H105" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
@@ -15381,22 +15569,22 @@
     <row r="106" ht="28" customHeight="1">
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>W50S85-26-B-A007</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C106" s="40" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
@@ -15411,12 +15599,12 @@
       </c>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J106" s="17" t="inlineStr">
@@ -15433,12 +15621,12 @@
     <row r="107" ht="28" customHeight="1">
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>W912DR26BA007</t>
+          <t>140P9726Q0046</t>
         </is>
       </c>
       <c r="C107" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -15448,7 +15636,7 @@
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -15458,77 +15646,77 @@
       </c>
       <c r="G107" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H107" s="20" t="inlineStr">
         <is>
+          <t>Jun 25, 2026</t>
+        </is>
+      </c>
+      <c r="I107" s="20" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="J107" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K107" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>W50S85-26-B-A007</t>
+        </is>
+      </c>
+      <c r="C108" s="40" t="inlineStr">
+        <is>
+          <t>Feeder #7 Repair</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>Selfridge ANGB, Michigan</t>
+        </is>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>237130</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H108" s="17" t="inlineStr">
+        <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I107" s="20" t="inlineStr">
+      <c r="I108" s="17" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
       </c>
-      <c r="J107" s="20" t="inlineStr">
+      <c r="J108" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K107" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="B108" s="23" t="inlineStr">
-        <is>
-          <t>36C24726Q0610</t>
-        </is>
-      </c>
-      <c r="C108" s="28" t="inlineStr">
-        <is>
-          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
-        </is>
-      </c>
-      <c r="D108" s="23" t="inlineStr">
-        <is>
-          <t>Columbia, South Carolina</t>
-        </is>
-      </c>
-      <c r="E108" s="23" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F108" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G108" s="23" t="inlineStr">
-        <is>
-          <t>$47.0M</t>
-        </is>
-      </c>
-      <c r="H108" s="23" t="inlineStr">
-        <is>
-          <t>Jul 01, 2026</t>
-        </is>
-      </c>
-      <c r="I108" s="23" t="inlineStr">
-        <is>
-          <t>13d</t>
-        </is>
-      </c>
-      <c r="J108" s="23" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K108" s="36" t="inlineStr">
+      <c r="K108" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15537,12 +15725,12 @@
     <row r="109" ht="28" customHeight="1">
       <c r="B109" s="20" t="inlineStr">
         <is>
-          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
+          <t>W912DR26BA007</t>
         </is>
       </c>
       <c r="C109" s="37" t="inlineStr">
         <is>
-          <t>Repair Hush House Concrete B3857</t>
+          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -15552,7 +15740,7 @@
       </c>
       <c r="E109" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -15562,17 +15750,17 @@
       </c>
       <c r="G109" s="20" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H109" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I109" s="20" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="J109" s="20" t="inlineStr">
@@ -15587,52 +15775,52 @@
       </c>
     </row>
     <row r="110" ht="28" customHeight="1">
-      <c r="B110" s="17" t="inlineStr">
-        <is>
-          <t>W9133L26BA010</t>
-        </is>
-      </c>
-      <c r="C110" s="40" t="inlineStr">
-        <is>
-          <t>Air National Guard (ANG) Smart Meters</t>
-        </is>
-      </c>
-      <c r="D110" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E110" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F110" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>$4.2M</t>
-        </is>
-      </c>
-      <c r="H110" s="17" t="inlineStr">
-        <is>
-          <t>Jul 02, 2026</t>
-        </is>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>14d</t>
-        </is>
-      </c>
-      <c r="J110" s="17" t="inlineStr">
+      <c r="B110" s="23" t="inlineStr">
+        <is>
+          <t>36C24726Q0610</t>
+        </is>
+      </c>
+      <c r="C110" s="28" t="inlineStr">
+        <is>
+          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
+        </is>
+      </c>
+      <c r="D110" s="23" t="inlineStr">
+        <is>
+          <t>Columbia, South Carolina</t>
+        </is>
+      </c>
+      <c r="E110" s="23" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F110" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr">
+        <is>
+          <t>$47.0M</t>
+        </is>
+      </c>
+      <c r="H110" s="23" t="inlineStr">
+        <is>
+          <t>Jul 01, 2026</t>
+        </is>
+      </c>
+      <c r="I110" s="23" t="inlineStr">
+        <is>
+          <t>13d</t>
+        </is>
+      </c>
+      <c r="J110" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K110" s="42" t="inlineStr">
+      <c r="K110" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15641,12 +15829,12 @@
     <row r="111" ht="28" customHeight="1">
       <c r="B111" s="20" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
         </is>
       </c>
       <c r="C111" s="37" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t>Repair Hush House Concrete B3857</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -15666,17 +15854,17 @@
       </c>
       <c r="G111" s="20" t="inlineStr">
         <is>
-          <t>$12.9M</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="H111" s="20" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
@@ -15691,52 +15879,52 @@
       </c>
     </row>
     <row r="112" ht="28" customHeight="1">
-      <c r="B112" s="23" t="inlineStr">
-        <is>
-          <t>36C24626R0067</t>
-        </is>
-      </c>
-      <c r="C112" s="28" t="inlineStr">
-        <is>
-          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
-        </is>
-      </c>
-      <c r="D112" s="23" t="inlineStr">
-        <is>
-          <t>Hampton, Virginia</t>
-        </is>
-      </c>
-      <c r="E112" s="23" t="inlineStr">
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>W9133L26BA010</t>
+        </is>
+      </c>
+      <c r="C112" s="40" t="inlineStr">
+        <is>
+          <t>Air National Guard (ANG) Smart Meters</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F112" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G112" s="23" t="inlineStr">
-        <is>
-          <t>$7.0M</t>
-        </is>
-      </c>
-      <c r="H112" s="23" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I112" s="23" t="inlineStr">
-        <is>
-          <t>25d</t>
-        </is>
-      </c>
-      <c r="J112" s="23" t="inlineStr">
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>$4.2M</t>
+        </is>
+      </c>
+      <c r="H112" s="17" t="inlineStr">
+        <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="J112" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K112" s="36" t="inlineStr">
+      <c r="K112" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15745,12 +15933,12 @@
     <row r="113" ht="28" customHeight="1">
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0004</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="C113" s="37" t="inlineStr">
         <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -15760,7 +15948,7 @@
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -15770,77 +15958,77 @@
       </c>
       <c r="G113" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
+          <t>Jul 07, 2026</t>
+        </is>
+      </c>
+      <c r="I113" s="20" t="inlineStr">
+        <is>
+          <t>19d</t>
+        </is>
+      </c>
+      <c r="J113" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K113" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>36C24626R0067</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+        </is>
+      </c>
+      <c r="D114" s="23" t="inlineStr">
+        <is>
+          <t>Hampton, Virginia</t>
+        </is>
+      </c>
+      <c r="E114" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>$7.0M</t>
+        </is>
+      </c>
+      <c r="H114" s="23" t="inlineStr">
+        <is>
           <t>Jul 13, 2026</t>
         </is>
       </c>
-      <c r="I113" s="20" t="inlineStr">
+      <c r="I114" s="23" t="inlineStr">
         <is>
           <t>25d</t>
         </is>
       </c>
-      <c r="J113" s="20" t="inlineStr">
+      <c r="J114" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K113" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="28" customHeight="1">
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>140L2626Q0032</t>
-        </is>
-      </c>
-      <c r="C114" s="40" t="inlineStr">
-        <is>
-          <t>Y--Indian Springs Vault Toilet</t>
-        </is>
-      </c>
-      <c r="D114" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E114" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F114" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H114" s="17" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>25d</t>
-        </is>
-      </c>
-      <c r="J114" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K114" s="42" t="inlineStr">
+      <c r="K114" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15849,22 +16037,22 @@
     <row r="115" ht="28" customHeight="1">
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>W912EE26RA015</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C115" s="37" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -15879,12 +16067,12 @@
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
@@ -15901,12 +16089,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>140R4025R0017</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C116" s="40" t="inlineStr">
         <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+          <t>Y--Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D116" s="17" t="inlineStr">
@@ -15916,7 +16104,7 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
@@ -15931,12 +16119,12 @@
       </c>
       <c r="H116" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J116" s="17" t="inlineStr">
@@ -15953,22 +16141,22 @@
     <row r="117" ht="28" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C117" s="37" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -15983,12 +16171,12 @@
       </c>
       <c r="H117" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
@@ -16005,12 +16193,12 @@
     <row r="118" ht="28" customHeight="1">
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140R4025R0017</t>
         </is>
       </c>
       <c r="C118" s="40" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
       <c r="D118" s="17" t="inlineStr">
@@ -16020,7 +16208,7 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
@@ -16035,12 +16223,12 @@
       </c>
       <c r="H118" s="17" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="J118" s="17" t="inlineStr">
@@ -16057,12 +16245,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C119" s="37" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
@@ -16072,7 +16260,7 @@
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -16087,12 +16275,12 @@
       </c>
       <c r="H119" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
@@ -16109,12 +16297,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C120" s="40" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D120" s="17" t="inlineStr">
@@ -16139,12 +16327,12 @@
       </c>
       <c r="H120" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="J120" s="17" t="inlineStr">
@@ -16161,12 +16349,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C121" s="37" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -16213,12 +16401,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C122" s="40" t="inlineStr">
         <is>
-          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D122" s="17" t="inlineStr">
@@ -16228,7 +16416,7 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
@@ -16238,17 +16426,17 @@
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H122" s="17" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
-          <t>39d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J122" s="17" t="inlineStr">
@@ -16265,22 +16453,22 @@
     <row r="123" ht="28" customHeight="1">
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00029</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C123" s="37" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
@@ -16290,17 +16478,17 @@
       </c>
       <c r="G123" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H123" s="20" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
@@ -16317,12 +16505,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>140L3726R0006</t>
+          <t>140FGA26R0024</t>
         </is>
       </c>
       <c r="C124" s="40" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
@@ -16332,87 +16520,87 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="H124" s="17" t="inlineStr">
+        <is>
+          <t>Jul 27, 2026</t>
+        </is>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>39d</t>
+        </is>
+      </c>
+      <c r="J124" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K124" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>75H70126R00029</t>
+        </is>
+      </c>
+      <c r="C125" s="37" t="inlineStr">
+        <is>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+        </is>
+      </c>
+      <c r="D125" s="20" t="inlineStr">
+        <is>
+          <t>Pine Ridge, South Dakota</t>
+        </is>
+      </c>
+      <c r="E125" s="20" t="inlineStr">
+        <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F124" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G124" s="17" t="inlineStr">
-        <is>
-          <t>$19.0M</t>
-        </is>
-      </c>
-      <c r="H124" s="17" t="inlineStr">
-        <is>
-          <t>Aug 28, 2026</t>
-        </is>
-      </c>
-      <c r="I124" s="17" t="inlineStr">
-        <is>
-          <t>71d</t>
-        </is>
-      </c>
-      <c r="J124" s="17" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G125" s="20" t="inlineStr">
+        <is>
+          <t>$3.0M</t>
+        </is>
+      </c>
+      <c r="H125" s="20" t="inlineStr">
+        <is>
+          <t>Jul 31, 2026</t>
+        </is>
+      </c>
+      <c r="I125" s="20" t="inlineStr">
+        <is>
+          <t>43d</t>
+        </is>
+      </c>
+      <c r="J125" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K124" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="B125" s="23" t="inlineStr">
-        <is>
-          <t>36C25026B0045</t>
-        </is>
-      </c>
-      <c r="C125" s="28" t="inlineStr">
-        <is>
-          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
-        </is>
-      </c>
-      <c r="D125" s="23" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio</t>
-        </is>
-      </c>
-      <c r="E125" s="23" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F125" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t>$750K</t>
-        </is>
-      </c>
-      <c r="H125" s="23" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I125" s="23" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J125" s="23" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K125" s="36" t="inlineStr">
+      <c r="K125" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16421,12 +16609,12 @@
     <row r="126" ht="28" customHeight="1">
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>W911WN26RA011</t>
+          <t>140L3726R0006</t>
         </is>
       </c>
       <c r="C126" s="40" t="inlineStr">
         <is>
-          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
@@ -16436,7 +16624,7 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -16446,77 +16634,77 @@
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="H126" s="17" t="inlineStr">
         <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>71d</t>
+        </is>
+      </c>
+      <c r="J126" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K126" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="B127" s="23" t="inlineStr">
+        <is>
+          <t>36C25026B0045</t>
+        </is>
+      </c>
+      <c r="C127" s="28" t="inlineStr">
+        <is>
+          <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
+        </is>
+      </c>
+      <c r="D127" s="23" t="inlineStr">
+        <is>
+          <t>Dayton, Ohio</t>
+        </is>
+      </c>
+      <c r="E127" s="23" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F127" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
           <t>Jun 18, 2026</t>
         </is>
       </c>
-      <c r="I126" s="17" t="inlineStr">
+      <c r="I127" s="23" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="J126" s="17" t="inlineStr">
+      <c r="J127" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K126" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="28" customHeight="1">
-      <c r="B127" s="20" t="inlineStr">
-        <is>
-          <t>140P6026Q0052</t>
-        </is>
-      </c>
-      <c r="C127" s="37" t="inlineStr">
-        <is>
-          <t>Z--WACO Emergency Generator</t>
-        </is>
-      </c>
-      <c r="D127" s="20" t="inlineStr">
-        <is>
-          <t>Waco, Texas</t>
-        </is>
-      </c>
-      <c r="E127" s="20" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F127" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G127" s="20" t="inlineStr">
-        <is>
-          <t>$62K</t>
-        </is>
-      </c>
-      <c r="H127" s="20" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I127" s="20" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J127" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K127" s="39" t="inlineStr">
+      <c r="K127" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16525,12 +16713,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>W911WN26RA011</t>
         </is>
       </c>
       <c r="C128" s="40" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
@@ -16540,7 +16728,7 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -16555,12 +16743,12 @@
       </c>
       <c r="H128" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J128" s="17" t="inlineStr">
@@ -16575,52 +16763,52 @@
       </c>
     </row>
     <row r="129" ht="28" customHeight="1">
-      <c r="B129" s="23" t="inlineStr">
-        <is>
-          <t>36C25726B0007</t>
-        </is>
-      </c>
-      <c r="C129" s="28" t="inlineStr">
-        <is>
-          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
-        </is>
-      </c>
-      <c r="D129" s="23" t="inlineStr">
+      <c r="B129" s="20" t="inlineStr">
+        <is>
+          <t>140P6026Q0052</t>
+        </is>
+      </c>
+      <c r="C129" s="37" t="inlineStr">
+        <is>
+          <t>Z--WACO Emergency Generator</t>
+        </is>
+      </c>
+      <c r="D129" s="20" t="inlineStr">
         <is>
           <t>Waco, Texas</t>
         </is>
       </c>
-      <c r="E129" s="23" t="inlineStr">
+      <c r="E129" s="20" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F129" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G129" s="23" t="inlineStr">
-        <is>
-          <t>$2.5B</t>
-        </is>
-      </c>
-      <c r="H129" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I129" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" s="23" t="inlineStr">
+      <c r="F129" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G129" s="20" t="inlineStr">
+        <is>
+          <t>$62K</t>
+        </is>
+      </c>
+      <c r="H129" s="20" t="inlineStr">
+        <is>
+          <t>Jun 18, 2026</t>
+        </is>
+      </c>
+      <c r="I129" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="J129" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K129" s="36" t="inlineStr">
+      <c r="K129" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16629,12 +16817,12 @@
     <row r="130" ht="28" customHeight="1">
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C130" s="40" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
@@ -16644,7 +16832,7 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -16679,52 +16867,52 @@
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
-      <c r="B131" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26BA013</t>
-        </is>
-      </c>
-      <c r="C131" s="37" t="inlineStr">
-        <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
-        </is>
-      </c>
-      <c r="D131" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E131" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F131" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G131" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H131" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I131" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J131" s="20" t="inlineStr">
+      <c r="B131" s="23" t="inlineStr">
+        <is>
+          <t>36C25726B0007</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="inlineStr">
+        <is>
+          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
+        </is>
+      </c>
+      <c r="D131" s="23" t="inlineStr">
+        <is>
+          <t>Waco, Texas</t>
+        </is>
+      </c>
+      <c r="E131" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F131" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t>$2.5B</t>
+        </is>
+      </c>
+      <c r="H131" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K131" s="39" t="inlineStr">
+      <c r="K131" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16733,17 +16921,17 @@
     <row r="132" ht="28" customHeight="1">
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA008</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C132" s="40" t="inlineStr">
         <is>
-          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D132" s="17" t="inlineStr">
         <is>
-          <t>Saltsburg, Pennsylvania</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
@@ -16758,7 +16946,7 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
@@ -16785,12 +16973,12 @@
     <row r="133" ht="28" customHeight="1">
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C133" s="37" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -16810,7 +16998,7 @@
       </c>
       <c r="G133" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H133" s="20" t="inlineStr">
@@ -16837,22 +17025,22 @@
     <row r="134" ht="28" customHeight="1">
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>W911WN26BA008</t>
         </is>
       </c>
       <c r="C134" s="40" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
         </is>
       </c>
       <c r="D134" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Saltsburg, Pennsylvania</t>
         </is>
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
@@ -16862,7 +17050,7 @@
       </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H134" s="17" t="inlineStr">
@@ -16889,12 +17077,12 @@
     <row r="135" ht="28" customHeight="1">
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>W9128F26RA107</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C135" s="37" t="inlineStr">
         <is>
-          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
@@ -16904,87 +17092,87 @@
       </c>
       <c r="E135" s="20" t="inlineStr">
         <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F135" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G135" s="20" t="inlineStr">
+        <is>
+          <t>$3.0M</t>
+        </is>
+      </c>
+      <c r="H135" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J135" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K135" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>140FGA26R0028</t>
+        </is>
+      </c>
+      <c r="C136" s="40" t="inlineStr">
+        <is>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F135" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G135" s="20" t="inlineStr">
-        <is>
-          <t>$30.0M</t>
-        </is>
-      </c>
-      <c r="H135" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I135" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J135" s="20" t="inlineStr">
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G136" s="17" t="inlineStr">
+        <is>
+          <t>$11.8M</t>
+        </is>
+      </c>
+      <c r="H136" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J136" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K135" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="28" customHeight="1">
-      <c r="B136" s="23" t="inlineStr">
-        <is>
-          <t>36C24226B0057</t>
-        </is>
-      </c>
-      <c r="C136" s="28" t="inlineStr">
-        <is>
-          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
-        </is>
-      </c>
-      <c r="D136" s="23" t="inlineStr">
-        <is>
-          <t>Buffalo, New York</t>
-        </is>
-      </c>
-      <c r="E136" s="23" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="F136" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G136" s="23" t="inlineStr">
-        <is>
-          <t>$16.2M</t>
-        </is>
-      </c>
-      <c r="H136" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I136" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J136" s="23" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K136" s="36" t="inlineStr">
+      <c r="K136" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16993,17 +17181,17 @@
     <row r="137" ht="28" customHeight="1">
       <c r="B137" s="20" t="inlineStr">
         <is>
-          <t>140P6326B0008</t>
+          <t>W9128F26RA107</t>
         </is>
       </c>
       <c r="C137" s="37" t="inlineStr">
         <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>Medora, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E137" s="20" t="inlineStr">
@@ -17018,7 +17206,7 @@
       </c>
       <c r="G137" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$30.0M</t>
         </is>
       </c>
       <c r="H137" s="20" t="inlineStr">
@@ -17043,52 +17231,52 @@
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
-      <c r="B138" s="17" t="inlineStr">
-        <is>
-          <t>W912DQ26QA063</t>
-        </is>
-      </c>
-      <c r="C138" s="40" t="inlineStr">
-        <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
-        </is>
-      </c>
-      <c r="D138" s="17" t="inlineStr">
-        <is>
-          <t>Stockton, Missouri</t>
-        </is>
-      </c>
-      <c r="E138" s="17" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F138" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G138" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H138" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I138" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J138" s="17" t="inlineStr">
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>36C24226B0057</t>
+        </is>
+      </c>
+      <c r="C138" s="28" t="inlineStr">
+        <is>
+          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
+        </is>
+      </c>
+      <c r="D138" s="23" t="inlineStr">
+        <is>
+          <t>Buffalo, New York</t>
+        </is>
+      </c>
+      <c r="E138" s="23" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="F138" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G138" s="23" t="inlineStr">
+        <is>
+          <t>$16.2M</t>
+        </is>
+      </c>
+      <c r="H138" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I138" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K138" s="42" t="inlineStr">
+      <c r="K138" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -17097,17 +17285,17 @@
     <row r="139" ht="28" customHeight="1">
       <c r="B139" s="20" t="inlineStr">
         <is>
-          <t>W912WJ26QA124</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C139" s="37" t="inlineStr">
         <is>
-          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E139" s="20" t="inlineStr">
@@ -17122,7 +17310,7 @@
       </c>
       <c r="G139" s="20" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H139" s="20" t="inlineStr">
@@ -17149,22 +17337,22 @@
     <row r="140" ht="28" customHeight="1">
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>12445526Q0069</t>
+          <t>W912DQ26QA063</t>
         </is>
       </c>
       <c r="C140" s="40" t="inlineStr">
         <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
         </is>
       </c>
       <c r="D140" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stockton, Missouri</t>
         </is>
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
@@ -17174,22 +17362,22 @@
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>$25K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H140" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J140" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K140" s="42" t="inlineStr">
@@ -17201,12 +17389,12 @@
     <row r="141" ht="28" customHeight="1">
       <c r="B141" s="20" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>W912WJ26QA124</t>
         </is>
       </c>
       <c r="C141" s="37" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
@@ -17216,7 +17404,7 @@
       </c>
       <c r="E141" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -17226,22 +17414,22 @@
       </c>
       <c r="G141" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H141" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I141" s="20" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J141" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K141" s="39" t="inlineStr">
@@ -17253,57 +17441,213 @@
     <row r="142" ht="28" customHeight="1">
       <c r="B142" s="17" t="inlineStr">
         <is>
+          <t>12445526Q0069</t>
+        </is>
+      </c>
+      <c r="C142" s="40" t="inlineStr">
+        <is>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="J142" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K142" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="B143" s="20" t="inlineStr">
+        <is>
+          <t>SP470525R002026</t>
+        </is>
+      </c>
+      <c r="C143" s="37" t="inlineStr">
+        <is>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+        </is>
+      </c>
+      <c r="D143" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E143" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F143" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G143" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="20" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I143" s="20" t="inlineStr">
+        <is>
+          <t>12d</t>
+        </is>
+      </c>
+      <c r="J143" s="20" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K143" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>140R6026R0016</t>
+        </is>
+      </c>
+      <c r="C144" s="40" t="inlineStr">
+        <is>
+          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>$7.5M</t>
+        </is>
+      </c>
+      <c r="H144" s="17" t="inlineStr">
+        <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>53d</t>
+        </is>
+      </c>
+      <c r="J144" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K144" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="B145" s="20" t="inlineStr">
+        <is>
           <t>W9127826RA025</t>
         </is>
       </c>
-      <c r="C142" s="40" t="inlineStr">
+      <c r="C145" s="37" t="inlineStr">
         <is>
           <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
-      <c r="D142" s="17" t="inlineStr">
+      <c r="D145" s="20" t="inlineStr">
         <is>
           <t>Cape Canaveral, Florida</t>
         </is>
       </c>
-      <c r="E142" s="17" t="inlineStr">
+      <c r="E145" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F142" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G142" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H142" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I142" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J142" s="17" t="inlineStr">
+      <c r="F145" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G145" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H145" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J145" s="20" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="K142" s="42" t="inlineStr">
+      <c r="K145" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K142"/>
+  <autoFilter ref="B5:K145"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -17446,6 +17790,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17458,7 +17805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K78"/>
+  <dimension ref="B2:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -17486,7 +17833,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="47" t="inlineStr">
         <is>
-          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  73 records  (11 SDVOSB)  ·  June 17, 2026</t>
+          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  74 records  (11 SDVOSB)  ·  June 17, 2026</t>
         </is>
       </c>
     </row>
@@ -19210,12 +19557,12 @@
     <row r="38" ht="28" customHeight="1">
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C38" s="40" t="inlineStr">
         <is>
-          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
@@ -19230,17 +19577,17 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>Jun 29, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
@@ -19262,17 +19609,17 @@
     <row r="39" ht="28" customHeight="1">
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C39" s="55" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D39" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E39" s="56" t="inlineStr">
@@ -19282,7 +19629,7 @@
       </c>
       <c r="F39" s="56" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="56" t="inlineStr">
@@ -19319,12 +19666,12 @@
       </c>
       <c r="C40" s="40" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
@@ -19366,12 +19713,12 @@
     <row r="41" ht="28" customHeight="1">
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C41" s="55" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable Replacement</t>
+          <t>Y--GLBA REHAB WATERLINE</t>
         </is>
       </c>
       <c r="D41" s="56" t="inlineStr">
@@ -19391,12 +19738,12 @@
       </c>
       <c r="G41" s="56" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jul 01, 2026</t>
         </is>
       </c>
       <c r="H41" s="56" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="I41" s="56" t="inlineStr">
@@ -19418,12 +19765,12 @@
     <row r="42" ht="28" customHeight="1">
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C42" s="40" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
@@ -19438,17 +19785,17 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>Jul 01, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
@@ -19475,7 +19822,7 @@
       </c>
       <c r="C43" s="55" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
         </is>
       </c>
       <c r="D43" s="56" t="inlineStr">
@@ -19490,17 +19837,17 @@
       </c>
       <c r="F43" s="56" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="56" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jul 06, 2026</t>
         </is>
       </c>
       <c r="H43" s="56" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>18d</t>
         </is>
       </c>
       <c r="I43" s="56" t="inlineStr">
@@ -19508,9 +19855,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J43" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J43" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K43" s="57" t="inlineStr">
@@ -19522,12 +19869,12 @@
     <row r="44" ht="28" customHeight="1">
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C44" s="40" t="inlineStr">
         <is>
-          <t>Cottonwood Substation Construction, Stage 02, Phas</t>
+          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
@@ -19574,12 +19921,12 @@
     <row r="45" ht="28" customHeight="1">
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C45" s="55" t="inlineStr">
         <is>
-          <t>Replacement Maintenance Shop Fire Alarm Control Pa</t>
+          <t>MELSTONE DAM LIVESTOCK WATER SUPPLY</t>
         </is>
       </c>
       <c r="D45" s="56" t="inlineStr">
@@ -19631,7 +19978,7 @@
       </c>
       <c r="C46" s="40" t="inlineStr">
         <is>
-          <t>MELSTONE DAM LIVESTOCK WATER SUPPLY</t>
+          <t>Unidirectional Hydrant Flushing and Repair Program</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -19646,7 +19993,7 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
@@ -19678,12 +20025,12 @@
     <row r="47" ht="28" customHeight="1">
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C47" s="55" t="inlineStr">
         <is>
-          <t>Unidirectional Hydrant Flushing and Repair Program</t>
+          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
         </is>
       </c>
       <c r="D47" s="56" t="inlineStr">
@@ -19698,17 +20045,17 @@
       </c>
       <c r="F47" s="56" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="56" t="inlineStr">
         <is>
-          <t>Jul 06, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="H47" s="56" t="inlineStr">
         <is>
-          <t>18d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="I47" s="56" t="inlineStr">
@@ -19730,12 +20077,12 @@
     <row r="48" ht="28" customHeight="1">
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C48" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RELOCATABLE FACILITY (RFL) MAINTENANCE AND REPAIR SERVICES - EGLIN AFB </t>
+          <t>MN-UPR MS RIV NATL WILDL-WELL REPAIRS</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -19755,12 +20102,12 @@
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>Jul 07, 2026</t>
+          <t>Jul 08, 2026</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
@@ -20042,17 +20389,17 @@
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C54" s="40" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>U.S. ARMY 63RD READINESS DIVISION MILCON ERCIP MICROGRID</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
@@ -20062,7 +20409,7 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
@@ -20099,12 +20446,12 @@
       </c>
       <c r="C55" s="55" t="inlineStr">
         <is>
-          <t>Pompeys Pillar Security System Upgrade</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="D55" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="E55" s="56" t="inlineStr">
@@ -20146,12 +20493,12 @@
     <row r="56" ht="28" customHeight="1">
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C56" s="40" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Pompeys Pillar Security System Upgrade</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -20171,12 +20518,12 @@
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
@@ -20198,12 +20545,12 @@
     <row r="57" ht="28" customHeight="1">
       <c r="B57" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C57" s="55" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D57" s="56" t="inlineStr">
@@ -20250,17 +20597,17 @@
     <row r="58" ht="28" customHeight="1">
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
@@ -20302,17 +20649,17 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D59" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E59" s="56" t="inlineStr">
@@ -20327,12 +20674,12 @@
       </c>
       <c r="G59" s="56" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H59" s="56" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="I59" s="56" t="inlineStr">
@@ -20359,12 +20706,12 @@
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>Water Tank Storage</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -20374,17 +20721,17 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>Jul 20, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
@@ -20392,9 +20739,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J60" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J60" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K60" s="42" t="inlineStr">
@@ -20406,17 +20753,17 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D61" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="E61" s="56" t="inlineStr">
@@ -20426,17 +20773,17 @@
       </c>
       <c r="F61" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="G61" s="56" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jul 20, 2026</t>
         </is>
       </c>
       <c r="H61" s="56" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="I61" s="56" t="inlineStr">
@@ -20444,9 +20791,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J61" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J61" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K61" s="57" t="inlineStr">
@@ -20463,7 +20810,7 @@
       </c>
       <c r="C62" s="40" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>Z--EO 14398 - GAOA - National Elk Refuge Electrical R</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -20483,17 +20830,17 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="J62" s="18" t="inlineStr">
@@ -20510,17 +20857,17 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="54" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D63" s="56" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E63" s="56" t="inlineStr">
@@ -20567,12 +20914,12 @@
       </c>
       <c r="C64" s="40" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -20582,7 +20929,7 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -20614,17 +20961,17 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D65" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E65" s="56" t="inlineStr">
@@ -20634,17 +20981,17 @@
       </c>
       <c r="F65" s="56" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G65" s="56" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H65" s="56" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="I65" s="56" t="inlineStr">
@@ -20671,7 +21018,7 @@
       </c>
       <c r="C66" s="40" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -20686,17 +21033,17 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
@@ -20718,17 +21065,17 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="54" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D67" s="56" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E67" s="56" t="inlineStr">
@@ -20743,12 +21090,12 @@
       </c>
       <c r="G67" s="56" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="H67" s="56" t="inlineStr">
         <is>
-          <t>12d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="I67" s="56" t="inlineStr">
@@ -20770,17 +21117,17 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C68" s="40" t="inlineStr">
         <is>
-          <t>Air National Guard (ANG) Smart Meters</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -20790,17 +21137,17 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>$4.2M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>12d</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
@@ -20822,17 +21169,17 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="54" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Air National Guard (ANG) Smart Meters</t>
         </is>
       </c>
       <c r="D69" s="56" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E69" s="56" t="inlineStr">
@@ -20842,17 +21189,17 @@
       </c>
       <c r="F69" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$4.2M</t>
         </is>
       </c>
       <c r="G69" s="56" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="H69" s="56" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="I69" s="56" t="inlineStr">
@@ -20860,9 +21207,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J69" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K69" s="57" t="inlineStr">
@@ -20874,17 +21221,17 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C70" s="40" t="inlineStr">
         <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -20899,12 +21246,12 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
@@ -20931,7 +21278,7 @@
       </c>
       <c r="C71" s="55" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
       <c r="D71" s="56" t="inlineStr">
@@ -20951,12 +21298,12 @@
       </c>
       <c r="G71" s="56" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="H71" s="56" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="I71" s="56" t="inlineStr">
@@ -20964,9 +21311,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J71" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J71" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K71" s="57" t="inlineStr">
@@ -20983,7 +21330,7 @@
       </c>
       <c r="C72" s="40" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
@@ -21030,17 +21377,17 @@
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C73" s="55" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D73" s="56" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E73" s="56" t="inlineStr">
@@ -21050,17 +21397,17 @@
       </c>
       <c r="F73" s="56" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="56" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H73" s="56" t="inlineStr">
         <is>
-          <t>43d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="I73" s="56" t="inlineStr">
@@ -21087,12 +21434,12 @@
       </c>
       <c r="C74" s="40" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -21102,17 +21449,17 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>71d</t>
+          <t>43d</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
@@ -21139,12 +21486,12 @@
       </c>
       <c r="C75" s="55" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D75" s="56" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E75" s="56" t="inlineStr">
@@ -21154,17 +21501,17 @@
       </c>
       <c r="F75" s="56" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G75" s="56" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H75" s="56" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>71d</t>
         </is>
       </c>
       <c r="I75" s="56" t="inlineStr">
@@ -21172,9 +21519,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J75" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J75" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K75" s="57" t="inlineStr">
@@ -21186,17 +21533,17 @@
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C76" s="40" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -21206,17 +21553,17 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
@@ -21224,9 +21571,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J76" s="44" t="inlineStr">
-        <is>
-          <t>Pre-Sol</t>
+      <c r="J76" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K76" s="42" t="inlineStr">
@@ -21243,12 +21590,12 @@
       </c>
       <c r="C77" s="55" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D77" s="56" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E77" s="56" t="inlineStr">
@@ -21290,57 +21637,109 @@
     <row r="78" ht="28" customHeight="1">
       <c r="B78" s="16" t="inlineStr">
         <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C78" s="40" t="inlineStr">
+        <is>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Stockton, Missouri</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J78" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K78" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="B79" s="54" t="inlineStr">
+        <is>
           <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
-      <c r="C78" s="40" t="inlineStr">
+      <c r="C79" s="55" t="inlineStr">
         <is>
           <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E78" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="17" t="inlineStr">
+      <c r="D79" s="56" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E79" s="56" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F79" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="56" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="H78" s="17" t="inlineStr">
+      <c r="H79" s="56" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
       </c>
-      <c r="I78" s="17" t="inlineStr">
+      <c r="I79" s="56" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="J78" s="18" t="inlineStr">
+      <c r="J79" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="K78" s="42" t="inlineStr">
+      <c r="K79" s="57" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K78"/>
+  <autoFilter ref="B5:K79"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -21419,6 +21818,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
